--- a/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0014.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0014.xlsx
@@ -834,7 +834,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>{Male=Ngài;Female=Nữ Ngài} Arbiter, liệu tiểu nhân có thể chuyển Giao Ước Thời Gian cho Jinhsi không?</t>
+          <t>{Male=Lord;Female=Lady} Arbiter, liệu tiểu nhân có thể chuyển Giao Ước Thời Gian cho Jinhsi không?</t>
         </is>
       </c>
     </row>
@@ -2914,7 +2914,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>Ngươi à, đồ to xác?! Hả?! Đồ trơ tráo, ta sẽ dạy cho ngươi biết tay...</t>
+          <t>Mày à, đồ to xác?! Hả?! Đồ trơ tráo, tao sẽ dạy cho mày biết tay...</t>
         </is>
       </c>
     </row>
@@ -3499,7 +3499,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>{Male=Ngài;Female=Nữ Ngài} Arbiter, ngài đã nghe về Bờ Biển Đen chưa?</t>
+          <t>{Male=Lord;Female=Lady} Arbiter, ngài đã nghe về Bờ Biển Đen chưa?</t>
         </is>
       </c>
     </row>
@@ -4019,7 +4019,7 @@
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>Có người đề nghị quay về Hồng Chân để đoàn tụ với các Cộng Hưởng Giả khác, {Male=Ngài;Female=Nữ} Arbiter à.</t>
+          <t>Có người đề nghị quay về Hồng Chân để đoàn tụ với các Cộng Hưởng Giả khác, {Male=Lord;Female=Lady} Arbiter à.</t>
         </is>
       </c>
     </row>
@@ -4344,7 +4344,7 @@
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>Đứa bé gái ấy chính là đứa trẻ đã chết, giờ tái sinh thành Quan Phủ của Kim Châu.</t>
+          <t>Đứa bé gái ấy chính là đứa trẻ đã chết, giờ tái sinh thành Quan Phủ của Jinzhou.</t>
         </is>
       </c>
     </row>
@@ -4669,7 +4669,7 @@
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>Cuối cùng, về chuyện Rover đó...</t>
+          <t>Cuối cùng, về chuyện Vận Mệnh Giả đó...</t>
         </is>
       </c>
     </row>
@@ -4864,7 +4864,7 @@
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>R?i ?i ngay. Kh?ng th? ?? m?t ng??i n?o ?? ph?i ch? qu? l?u sau song s?t.</t>
+          <t>Cút ngay đi. Không thể để một người nào đó phải chờ quá lâu sau song sắt.</t>
         </is>
       </c>
     </row>
@@ -5449,7 +5449,7 @@
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>Lần này, ta thấy nhiều hơn rồi.</t>
+          <t>Lần này, tao thấy nhiều hơn rồi.</t>
         </is>
       </c>
     </row>
@@ -5514,7 +5514,7 @@
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>Lần này, ta thấy thứ khác lạ.</t>
+          <t>Lần này, tao thấy thứ khác lạ.</t>
         </is>
       </c>
     </row>
@@ -5579,7 +5579,7 @@
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>Đợi đã, để ta hiểu cho rõ... Lính canh đã cuốn ngươi lên một ngọn núi hình con rồng à...</t>
+          <t>Đợi đã, để tao hiểu cho rõ... Lính canh đã cuốn mày lên một ngọn núi hình con rồng à...</t>
         </is>
       </c>
     </row>
@@ -6684,7 +6684,7 @@
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>Ta nghe nói có một đất nước tên là Ri... Rinas gì đó ấy. Dù sao thì, Echo ở đó đỉnh lắm.</t>
+          <t>Tao nghe nói có một đất nước tên là Ri... Rinas gì đó ấy. Dù sao thì, Echo ở đó đỉnh lắm.</t>
         </is>
       </c>
     </row>
@@ -7529,7 +7529,7 @@
       </c>
       <c r="M109" t="inlineStr">
         <is>
-          <t>Ta vừa nhớ lại cảnh nhìn thấy Sentinel của họ... Có lẽ chuyện đó xảy ra ở Núi Firmament...</t>
+          <t>Tao vừa nhớ lại cảnh nhìn thấy Sentinel của họ... Có lẽ chuyện đó xảy ra ở Núi Firmament...</t>
         </is>
       </c>
     </row>
@@ -9999,7 +9999,7 @@
       </c>
       <c r="M147" t="inlineStr">
         <is>
-          <t>{PlayerName}, nếu ta có ngã xuống... đừng lo cho ta.</t>
+          <t>{PlayerName}, nếu tao có ngã xuống... đừng lo cho tao.</t>
         </is>
       </c>
     </row>
@@ -10519,7 +10519,7 @@
       </c>
       <c r="M155" t="inlineStr">
         <is>
-          <t>Cậu đã mơ thấy Hồng Trấn à?</t>
+          <t>Cậu đã mơ thấy Hongzhen à?</t>
         </is>
       </c>
     </row>
@@ -10714,7 +10714,7 @@
       </c>
       <c r="M158" t="inlineStr">
         <is>
-          <t>Ta mơ thấy Hongzhen bị TD tấn công.</t>
+          <t>Tao mơ thấy Hongzhen bị TD tấn công.</t>
         </is>
       </c>
     </row>
@@ -10779,7 +10779,7 @@
       </c>
       <c r="M159" t="inlineStr">
         <is>
-          <t>Ta mơ thấy Sentinel bảo vệ mọi người ở đây.</t>
+          <t>Tao mơ thấy Sentinel bảo vệ mọi người ở đây.</t>
         </is>
       </c>
     </row>
@@ -10909,7 +10909,7 @@
       </c>
       <c r="M161" t="inlineStr">
         <is>
-          <t>Hơn một thế kỷ trước, một đoàn Tacet Discord khổng lồ đã tràn vào Huanglong. Hồng Trấn đã phải hứng chịu tổn thất nặng nề trong cuộc tấn công đó.</t>
+          <t>Hơn một thế kỷ trước, một đoàn Tacet Discord khổng lồ đã tràn vào Huanglong. Hongzhen đã phải hứng chịu tổn thất nặng nề trong cuộc tấn công đó.</t>
         </is>
       </c>
     </row>
@@ -11234,7 +11234,7 @@
       </c>
       <c r="M166" t="inlineStr">
         <is>
-          <t>Chúng đã giăng bẫy ở Hồng Trấn rồi.</t>
+          <t>Chúng đã giăng bẫy ở Hongzhen rồi.</t>
         </is>
       </c>
     </row>
@@ -11364,7 +11364,7 @@
       </c>
       <c r="M168" t="inlineStr">
         <is>
-          <t>Cái gì đây?</t>
+          <t>Cái gì vậy?</t>
         </is>
       </c>
     </row>
@@ -11494,7 +11494,7 @@
       </c>
       <c r="M170" t="inlineStr">
         <is>
-          <t>Dấu vết dẫn sâu hơn vào trung tâm Hồng Trấn.</t>
+          <t>Dấu vết dẫn sâu hơn vào trung tâm Hongzhen.</t>
         </is>
       </c>
     </row>
@@ -13769,7 +13769,7 @@
       </c>
       <c r="M205" t="inlineStr">
         <is>
-          <t>Chuyện gì đã xảy ra?</t>
+          <t>Chuyện gì đã xảy ra thế?</t>
         </is>
       </c>
     </row>
@@ -14094,7 +14094,7 @@
       </c>
       <c r="M210" t="inlineStr">
         <is>
-          <t>Vậy là Sentinel đã dùng sức mạnh của mình bảo vệ Hồng Trấn, nhưng lại không thể đưa mọi thứ trở lại bình thường sao?</t>
+          <t>Vậy là Sentinel đã dùng sức mạnh của mình bảo vệ Hongzhen, nhưng lại không thể đưa mọi thứ trở lại bình thường sao?</t>
         </is>
       </c>
     </row>
@@ -15134,7 +15134,7 @@
       </c>
       <c r="M226" t="inlineStr">
         <is>
-          <t>Hừm. Thế là cậu biến thành Clang Bang rồi à?</t>
+          <t>Hừm. Thế là mày biến thành Clang Bang rồi à?</t>
         </is>
       </c>
     </row>
@@ -17344,7 +17344,7 @@
       </c>
       <c r="M260" t="inlineStr">
         <is>
-          <t>—Họ viết rằng nó cũng tương tự như cách Cộng Hưởng Giả trải qua trạng thái Overclocking.</t>
+          <t>—Họ viết rằng nó cũng tương tự như cách Resonator trải qua trạng thái Overclocking.</t>
         </is>
       </c>
     </row>
@@ -17799,7 +17799,7 @@
       </c>
       <c r="M267" t="inlineStr">
         <is>
-          <t>Và đừng quên là nếu không có tôi đóng vai Người Dẫn Đường cho {PlayerName}, thì giờ đây chúng ta đã chẳng có {Male=anh ấy;Female=cô ấy} ở đây rồi.</t>
+          <t>Và đừng quên là nếu không có tôi đóng vai Người Dẫn Đường cho {PlayerName}, thì giờ đây chúng ta đã chẳng có {Male=him;Female=her} ở đây rồi.</t>
         </is>
       </c>
     </row>
@@ -17864,7 +17864,7 @@
       </c>
       <c r="M268" t="inlineStr">
         <is>
-          <t>{PlayerName} có mối liên kết sâu sắc với nơi này. Ngươi cần sự trợ giúp của {Male=anh ấy;Female=cô ấy} để giải quyết khủng hoảng ở Núi Firmament.</t>
+          <t>{PlayerName} có mối liên kết sâu sắc với nơi này. Ngươi cần sự trợ giúp của {Male=his;Female=her} để giải quyết khủng hoảng ở Núi Firmament.</t>
         </is>
       </c>
     </row>
@@ -18189,7 +18189,7 @@
       </c>
       <c r="M273" t="inlineStr">
         <is>
-          <t>Ra là vậy...</t>
+          <t>Ta hiểu rồi...</t>
         </is>
       </c>
     </row>
@@ -22869,7 +22869,7 @@
       </c>
       <c r="M345" t="inlineStr">
         <is>
-          <t>Ta sống cả đời ở Kim Châu mà chưa từng đặt chân đến Hồng Trấn, vậy mà đến cả ta cũng biết đến truyền thuyết đó.</t>
+          <t>Ta sống cả đời ở Jinzhou mà chưa từng đặt chân đến Hongzhen, vậy mà đến cả ta cũng biết đến truyền thuyết đó.</t>
         </is>
       </c>
     </row>
@@ -24689,7 +24689,7 @@
       </c>
       <c r="M373" t="inlineStr">
         <is>
-          <t>Nghĩ lại thì, từ khi ngươi đến Jinzhou, ta gặp được không ít điều tốt đẹp.</t>
+          <t>Nghĩ lại thì, từ khi mày đến Jinzhou, tao gặp được không ít điều tốt đẹp.</t>
         </is>
       </c>
     </row>
@@ -24949,7 +24949,7 @@
       </c>
       <c r="M377" t="inlineStr">
         <is>
-          <t>Ta sẽ đi cùng ngươi gặp Sentinel.</t>
+          <t>Tao sẽ đi cùng mày gặp Sentinel.</t>
         </is>
       </c>
     </row>
